--- a/data/trans_orig/IP31KM08_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM08_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26015</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19437</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>31811</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>48,43%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>36,18%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>59,22%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>25074</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>16392</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>33456</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>46,69%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>30,53%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>62,3%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>27088</t>
+          <t>26949</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20271</t>
+          <t>21546</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34594</t>
+          <t>32611</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>52162</t>
+          <t>52964</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41051</t>
+          <t>44203</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63296</t>
+          <t>61518</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>61,75%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>27700</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>21904</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>34278</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>51,57%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>40,78%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>63,82%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>28625</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>20243</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>37307</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>53,31%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>37,7%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>69,47%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31257</t>
+          <t>18956</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23751</t>
+          <t>13294</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38074</t>
+          <t>24359</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>59881</t>
+          <t>46656</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48747</t>
+          <t>38102</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70992</t>
+          <t>55417</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>55,63%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>212460</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>188088</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>230217</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>45,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>40,33%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>49,36%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>199276</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>158962</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>220766</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>44,1%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>35,18%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>48,86%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>225352</t>
+          <t>201983</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>201881</t>
+          <t>183463</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>248744</t>
+          <t>218489</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>424627</t>
+          <t>414444</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>380761</t>
+          <t>388238</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>457554</t>
+          <t>444656</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>49,9%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>253963</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>236206</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>278335</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>54,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>50,64%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>59,67%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>252556</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>231066</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>292870</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>55,9%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>51,14%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>64,82%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>279898</t>
+          <t>222683</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>256506</t>
+          <t>206177</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>303369</t>
+          <t>241203</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>532455</t>
+          <t>476646</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>499528</t>
+          <t>446434</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>576321</t>
+          <t>502852</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>56,43%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>75790</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>64509</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>86295</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>45,47%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>38,7%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>51,77%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>56322</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>46120</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>67254</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>38,53%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>31,55%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>46,01%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>81338</t>
+          <t>57527</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68599</t>
+          <t>47698</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94283</t>
+          <t>69086</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>137659</t>
+          <t>133316</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121422</t>
+          <t>119359</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>153919</t>
+          <t>149925</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,77%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>90896</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>80391</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>102177</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>54,53%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>48,23%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>61,3%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>89864</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>78932</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>100066</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>61,47%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>53,99%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>68,45%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>99801</t>
+          <t>89613</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86856</t>
+          <t>78054</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>112540</t>
+          <t>99442</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>189665</t>
+          <t>180509</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>173405</t>
+          <t>163900</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>205902</t>
+          <t>194466</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>61,97%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>314265</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>289722</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>339438</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>45,76%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>42,18%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>49,42%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>405</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>280672</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>239715</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>304589</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>36,78%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>46,74%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>333776</t>
+          <t>286459</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>305651</t>
+          <t>265055</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>361634</t>
+          <t>307741</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>614448</t>
+          <t>600724</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>570318</t>
+          <t>566496</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>652419</t>
+          <t>633926</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>48,59%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>372559</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>347386</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>397102</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>54,24%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>50,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>57,82%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>371045</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>347128</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>412002</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>53,26%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>63,22%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>410957</t>
+          <t>331252</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>383099</t>
+          <t>309970</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>439082</t>
+          <t>352656</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>782002</t>
+          <t>703811</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>744031</t>
+          <t>670609</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>826132</t>
+          <t>738039</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>56,57%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
